--- a/plot/data/raw/expert_rating_workbooks/专家4-专家评分——统计版.xlsx
+++ b/plot/data/raw/expert_rating_workbooks/专家4-专家评分——统计版.xlsx
@@ -117,7 +117,7 @@
     <t>答案解析评分</t>
   </si>
   <si>
-    <t>LLM总分</t>
+    <t>ULM总分</t>
   </si>
   <si>
     <t>该题是否为AI题</t>
